--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>17855.39</v>
+        <v>17668.4</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14950.77</v>
+        <v>14794.2</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>18250.02</v>
+        <v>18335.02</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2366.53</v>
+        <v>2377.56</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18639.15</v>
+        <v>18561.01</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>936.42</v>
+        <v>936.4299999999999</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38263.19</v>
+        <v>38513.96</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7822.87</v>
+        <v>7928.22</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1028.46</v>
+        <v>1037.62</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26349.88</v>
+        <v>26304.72</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1092.12</v>
+        <v>1087.23</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>976.4400000000001</v>
+        <v>972.0700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>772.15</v>
+        <v>767.21</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8466.84</v>
+        <v>8491.49</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>37669.97</v>
+        <v>38133.59</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>879.09</v>
+        <v>887.01</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>130.7</v>
+        <v>130.97</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>785.8099999999999</v>
+        <v>791.66</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3046.46</v>
+        <v>3013.32</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>31743.96</v>
+        <v>31547.15</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3496.26</v>
+        <v>3512.14</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>37440.71</v>
+        <v>37998.21</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>259.8</v>
+        <v>259.12</v>
       </c>
     </row>
     <row r="25">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>47105.53</v>
+        <v>46980.94</v>
       </c>
     </row>
     <row r="26">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>34462.24</v>
+        <v>34789.6</v>
       </c>
     </row>
     <row r="27">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>36331.3</v>
+        <v>36516.43</v>
       </c>
     </row>
     <row r="28">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>378.16</v>
+        <v>376.24</v>
       </c>
     </row>
     <row r="29">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5160.37</v>
+        <v>5171.37</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8218.040000000001</v>
+        <v>8275.549999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1259.15</v>
+        <v>1256.41</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2185.66</v>
+        <v>2160.23</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5112.69</v>
+        <v>5084.35</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4109.02</v>
+        <v>4136.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2291-1766-CM25</t>
+          <t>2436-497-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>17668.4</v>
+        <v>34264.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2291-1772-CM25</t>
+          <t>2436-565-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14794.2</v>
+        <v>1690.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1421-637-CM25</t>
+          <t>2436-829-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>18335.02</v>
+        <v>3671.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1469-3814-CM25</t>
+          <t>2291-1766-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FERMAT SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.814.662-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2377.56</v>
+        <v>17668.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1421-678-CM25</t>
+          <t>2291-1772-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18561.01</v>
+        <v>14794.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2436-24-CM26</t>
+          <t>1421-637-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>936.4299999999999</v>
+        <v>18335.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2436-60-CM26</t>
+          <t>1469-3814-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>FERMAT SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>77.814.662-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38513.96</v>
+        <v>2377.56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1199-25-CM26</t>
+          <t>1421-678-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7928.22</v>
+        <v>18561.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>362-76-CM26</t>
+          <t>2436-24-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1037.62</v>
+        <v>936.4299999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1421-79-CM26</t>
+          <t>2436-60-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26304.72</v>
+        <v>38513.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1426095-47-CM26</t>
+          <t>1199-25-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1087.23</v>
+        <v>7928.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2436-295-CM26</t>
+          <t>362-76-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>972.0700000000001</v>
+        <v>1037.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1426095-55-CM26</t>
+          <t>1421-79-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>767.21</v>
+        <v>26304.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079566-134-CM26</t>
+          <t>1426095-47-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8491.49</v>
+        <v>1087.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2436-416-CM26</t>
+          <t>2436-295-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>38133.59</v>
+        <v>972.0700000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4451-232-CM26</t>
+          <t>1426095-55-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FIRAMCO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.942.697-1</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>887.01</v>
+        <v>767.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057461-600-CM26</t>
+          <t>1079566-134-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>130.97</v>
+        <v>8491.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2291-813-CM26</t>
+          <t>2436-416-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>791.66</v>
+        <v>38133.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4451-272-CM26</t>
+          <t>4451-232-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3013.32</v>
+        <v>887.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2295-88-CM26</t>
+          <t>1057461-600-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,32 +1713,28 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.616.370-6</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>31547.15</v>
+        <v>130.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2291-1079-CM26</t>
+          <t>2291-813-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1778,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3512.14</v>
+        <v>791.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2436-694-CM26</t>
+          <t>4451-272-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>37998.21</v>
+        <v>3013.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057461-870-CM26</t>
+          <t>2295-88-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,28 +1896,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>78.616.370-6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>259.12</v>
+        <v>31547.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2295-92-SE26</t>
+          <t>2291-1079-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1961,32 +1961,28 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>10.991.344-8</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>46980.94</v>
+        <v>3512.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2298-545-CM26</t>
+          <t>2436-694-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1996,12 +1992,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2011,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2026,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2041,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>34789.6</v>
+        <v>37998.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2436-799-CM26</t>
+          <t>2295-92-SE26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2057,12 +2053,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2072,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2087,28 +2083,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>36516.43</v>
+        <v>46980.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057461-970-CM26</t>
+          <t>1057461-870-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2118,17 +2118,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>376.24</v>
+        <v>259.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2291-1205-CM26</t>
+          <t>2298-545-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>IMunicipalidad de Molina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2224,13 +2224,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5171.37</v>
+        <v>34789.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2595-265-CM26</t>
+          <t>2436-799-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2245,22 +2245,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8275.549999999999</v>
+        <v>36516.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2436-885-CM26</t>
+          <t>1057461-970-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1256.41</v>
+        <v>376.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4451-431-CM26</t>
+          <t>2291-1205-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2367,22 +2367,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2160.23</v>
+        <v>5171.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4451-440-CM26</t>
+          <t>2595-265-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5084.35</v>
+        <v>8275.549999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2595-307-CM26</t>
+          <t>2436-885-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2529,6 +2529,189 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
+        <v>1256.41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4451-431-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>2160.23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4451-440-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>5084.35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2595-307-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.130.700-K</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>4136.52</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2436-497-CM25</t>
+          <t>2595-8-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>34264.39</v>
+        <v>8580.309999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2436-565-CM25</t>
+          <t>1511-281-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1690.24</v>
+        <v>1938.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2436-829-CM25</t>
+          <t>2291-311-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3671.57</v>
+        <v>24949.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2291-1766-CM25</t>
+          <t>1057461-6636-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17668.4</v>
+        <v>365.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2291-1772-CM25</t>
+          <t>2436-497-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>14794.2</v>
+        <v>34264.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1421-637-CM25</t>
+          <t>2436-565-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>18335.02</v>
+        <v>1690.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1469-3814-CM25</t>
+          <t>2436-608-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FERMAT SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.814.662-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2377.56</v>
+        <v>1025.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1421-678-CM25</t>
+          <t>2436-619-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18561.01</v>
+        <v>3726.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2436-24-CM26</t>
+          <t>2291-781-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>936.4299999999999</v>
+        <v>24959.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2436-60-CM26</t>
+          <t>4451-305-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>38513.96</v>
+        <v>994.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1199-25-CM26</t>
+          <t>4451-321-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7928.22</v>
+        <v>1065.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>362-76-CM26</t>
+          <t>3399-108-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1037.62</v>
+        <v>71632.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1421-79-CM26</t>
+          <t>1426095-115-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>26304.72</v>
+        <v>637.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1426095-47-CM26</t>
+          <t>2436-708-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1087.23</v>
+        <v>420.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2436-295-CM26</t>
+          <t>2436-711-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>972.0700000000001</v>
+        <v>36376.94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1426095-55-CM26</t>
+          <t>2291-964-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>767.21</v>
+        <v>2154.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1079566-134-CM26</t>
+          <t>2291-1028-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8491.49</v>
+        <v>8587.700000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2436-416-CM26</t>
+          <t>2436-829-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>38133.59</v>
+        <v>3671.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4451-232-CM26</t>
+          <t>2436-948-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FIRAMCO SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.942.697-1</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>887.01</v>
+        <v>35613.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057461-600-CM26</t>
+          <t>1057461-7569-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>130.97</v>
+        <v>358.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2291-813-CM26</t>
+          <t>707420-84-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>791.66</v>
+        <v>2704.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4451-272-CM26</t>
+          <t>2436-1307-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3013.32</v>
+        <v>35006.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2295-88-CM26</t>
+          <t>3399-186-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,32 +1896,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.616.370-6</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>31547.15</v>
+        <v>98003.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2291-1079-CM26</t>
+          <t>2291-1766-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1961,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3512.14</v>
+        <v>17668.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2436-694-CM26</t>
+          <t>2291-1772-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>37998.21</v>
+        <v>14794.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2295-92-SE26</t>
+          <t>1421-637-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,32 +2079,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>46980.94</v>
+        <v>18335.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057461-870-CM26</t>
+          <t>1469-3814-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2118,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2148,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>FERMAT SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.814.662-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2163,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>259.12</v>
+        <v>2377.56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2298-545-CM26</t>
+          <t>1421-678-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2179,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2209,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2224,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>34789.6</v>
+        <v>18561.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2436-799-CM26</t>
+          <t>2436-24-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2240,17 +2232,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2270,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2285,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>36516.43</v>
+        <v>936.4299999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057461-970-CM26</t>
+          <t>2436-60-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2301,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2316,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2331,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2346,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>376.24</v>
+        <v>38513.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2291-1205-CM26</t>
+          <t>1199-25-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2362,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2377,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2392,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2407,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5171.37</v>
+        <v>7928.22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2595-265-CM26</t>
+          <t>362-76-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2423,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2438,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2453,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2468,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8275.549999999999</v>
+        <v>1037.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2436-885-CM26</t>
+          <t>1421-79-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2484,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2529,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1256.41</v>
+        <v>26304.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4451-431-CM26</t>
+          <t>1426095-47-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2545,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2560,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2575,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2590,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2160.23</v>
+        <v>1087.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4451-440-CM26</t>
+          <t>2436-295-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2606,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2636,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2651,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5084.35</v>
+        <v>972.0700000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2595-307-CM26</t>
+          <t>1426095-55-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2667,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2682,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2697,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2712,7 +2704,1296 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
+        <v>767.21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1079566-134-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.979.370-6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>8491.49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2436-416-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>38133.59</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4451-232-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>FIRAMCO SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.942.697-1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>887.01</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1057461-600-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>130.97</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2291-813-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>791.66</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4451-272-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>3013.32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2295-88-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>78.616.370-6</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>31547.15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2291-1079-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>10.991.344-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>3512.14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2436-694-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>37998.21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1057461-870-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>259.12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2295-92-SE26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>46980.94</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2298-545-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.110.100-2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>IMunicipalidad de Molina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>34789.6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2436-799-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>36516.43</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1057461-970-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>376.24</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2291-1205-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>5171.37</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2595-265-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.130.700-K</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>8275.549999999999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2436-885-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>1256.41</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4451-431-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>2160.23</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4451-440-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>5084.35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2595-307-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.130.700-K</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
         <v>4136.52</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2436-1073-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>36679.98</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2436-619-CM25</t>
+          <t>2291-781-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3726.01</v>
+        <v>24959.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2291-781-CM25</t>
+          <t>2436-619-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>24959.19</v>
+        <v>3726.01</v>
       </c>
     </row>
     <row r="11">
@@ -1917,7 +1917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2291-1766-CM25</t>
+          <t>2291-1772-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>17668.4</v>
+        <v>14794.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2291-1772-CM25</t>
+          <t>2291-1766-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>14794.2</v>
+        <v>17668.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1421-637-CM25</t>
+          <t>1469-3814-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>FERMAT SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.814.662-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>18335.02</v>
+        <v>2377.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1469-3814-CM25</t>
+          <t>1421-637-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FERMAT SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.814.662-2</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2377.56</v>
+        <v>18335.02</v>
       </c>
     </row>
     <row r="29">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3994,6 +3994,189 @@
       </c>
       <c r="M58" s="2" t="n">
         <v>36679.98</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1057461-1524-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>367.67</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2291-1517-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>2298.59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2291-1518-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>4536.31</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -562,7 +562,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1456,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1712,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2086,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2151,11 @@
           <t>77.814.662-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2216,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2411,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2476,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2602,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2667,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2732,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2797,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2927,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3118,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3374,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3498,7 +3626,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3681,7 +3813,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3878,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3925,7 +4065,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3986,7 +4130,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4108,7 +4256,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4169,7 +4321,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4335,6 +4335,71 @@
         <v>4536.31</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2436-1432-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>34759.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
